--- a/P4 Pengembangan Kebutuhan Perangkat Lunak/A Elisitasi/A4 Coding/20261021 Lembar_Coding_Codebook_1_0_2 (fenny).xlsx
+++ b/P4 Pengembangan Kebutuhan Perangkat Lunak/A Elisitasi/A4 Coding/20261021 Lembar_Coding_Codebook_1_0_2 (fenny).xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="401">
   <si>
     <t xml:space="preserve">Lembar Coding: Analisis Isi Krippendorff</t>
   </si>
@@ -214,328 +214,439 @@
     <t xml:space="preserve">Bagian</t>
   </si>
   <si>
+    <t xml:space="preserve">S4 - Subjek Data Pribadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R2 - Relevan langsung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T10 - Keamanan, Kerahasiaan, dan Penanganan Insiden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3 - Hak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F4 - Penyimpanan dan pengamanan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K2 - Non-fungsional: mutu data, kepatuhan, dan akuntabilitas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T14 - Larangan dan Perbuatan Melawan Hukum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T09 - Akuntabilitas, Pencatatan, dan Tata Kelola Kepatuhan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2 - Kewajiban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3 - Pengendali dan Prosesor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1 - Relevan tidak langsung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T06 - Aktivitas Pemrosesan dan Pengumpulan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4 - Pengecualian atau pembatasan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2 - Pengumpulan atau akuisisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K5 - Tidak menghasilkan kebutuhan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5 - Setiap Orang atau pihak umum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T11 - Retensi, Penghentian, Penghapusan, dan Pemusnahan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F6 - Retensi dan penghapusan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K4 - Batasan atau aturan bisnis hukum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T02 - Asas dan Prinsip Pemrosesan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P7 - Asas, prinsip, atau tujuan umum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1 - Perencanaan dan dasar pemrosesan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K3 - Fungsional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9 - Tidak ada subjek eksplisit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R0 - Tidak relevan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T16 - Urgensi, Konsep, dan Landasan Pelindungan Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1 - Pengendali Data Pribadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T07 - Data Pribadi Anak dan Kelompok Rentan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F7 - Tata kelola dan hak subjek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T13 - Transfer dan Pengalihan Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P5 - Kebolehan atau kewenangan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F3 - Pengolahan dan analisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T17 - Rujukan Regulasi Lain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P9 - Rujukan atau daftar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F8 - Lintas tahap atau tidak spesifik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T01 - Definisi, Istilah, dan Ruang Lingkup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6 - Definisi, klasifikasi, atau ruang lingkup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daftar kode sah (Codebook versi 1.0.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sumber: Bagian 6 sampai 7 codebook. Sheet ini dipakai oleh daftar pilihan (validasi data) pada lembar coding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengendali Data Pribadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosesor Data Pribadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengendali dan Prosesor</t>
+  </si>
+  <si>
     <t xml:space="preserve">S4</t>
   </si>
   <si>
+    <t xml:space="preserve">Subjek Data Pribadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setiap Orang atau pihak umum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instansi atau Badan Publik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lembaga atau Pemerintah (otoritas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penyelenggara sektor atau pihak lain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tidak ada subjek eksplisit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tidak relevan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relevan tidak langsung</t>
+  </si>
+  <si>
     <t xml:space="preserve">R2</t>
   </si>
   <si>
+    <t xml:space="preserve">Relevan langsung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definisi, Istilah, dan Ruang Lingkup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asas dan Prinsip Pemrosesan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jenis dan Klasifikasi Data Pribadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hak Subjek Data Pribadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dasar Pemrosesan dan Persetujuan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aktivitas Pemrosesan dan Pengumpulan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Pribadi Anak dan Kelompok Rentan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kualitas, Akurasi, dan Pembaruan Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akuntabilitas, Pencatatan, dan Tata Kelola Kepatuhan</t>
+  </si>
+  <si>
     <t xml:space="preserve">T10</t>
   </si>
   <si>
+    <t xml:space="preserve">Keamanan, Kerahasiaan, dan Penanganan Insiden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retensi, Penghentian, Penghapusan, dan Pemusnahan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengecualian dan Pembatasan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer dan Pengalihan Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larangan dan Perbuatan Melawan Hukum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akses dan Pemanfaatan Data Pemerintah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urgensi, Konsep, dan Landasan Pelindungan Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rujukan Regulasi Lain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lainnya (wajib jelaskan di V12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larangan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kewajiban</t>
+  </si>
+  <si>
     <t xml:space="preserve">P3</t>
   </si>
   <si>
+    <t xml:space="preserve">Hak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengecualian atau pembatasan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kebolehan atau kewenangan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definisi, klasifikasi, atau ruang lingkup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asas, prinsip, atau tujuan umum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deskriptif, argumentatif, atau rekomendasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rujukan atau daftar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perencanaan dan dasar pemrosesan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengumpulan atau akuisisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengolahan dan analisis</t>
+  </si>
+  <si>
     <t xml:space="preserve">F4</t>
   </si>
   <si>
+    <t xml:space="preserve">Penyimpanan dan pengamanan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penyebarluasan dan transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retensi dan penghapusan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata kelola dan hak subjek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lintas tahap atau tidak spesifik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-fungsional: keamanan dan kerahasiaan</t>
+  </si>
+  <si>
     <t xml:space="preserve">K2</t>
   </si>
   <si>
-    <t xml:space="preserve">T14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F2</t>
+    <t xml:space="preserve">Non-fungsional: mutu data, kepatuhan, dan akuntabilitas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fungsional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batasan atau aturan bisnis hukum</t>
   </si>
   <si>
     <t xml:space="preserve">K5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daftar kode sah (Codebook versi 1.0.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sumber: Bagian 6 sampai 7 codebook. Sheet ini dipakai oleh daftar pilihan (validasi data) pada lembar coding.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pengendali Data Pribadi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prosesor Data Pribadi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pengendali dan Prosesor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subjek Data Pribadi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setiap Orang atau pihak umum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instansi atau Badan Publik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lembaga atau Pemerintah (otoritas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penyelenggara sektor atau pihak lain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tidak ada subjek eksplisit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tidak relevan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relevan tidak langsung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relevan langsung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definisi, Istilah, dan Ruang Lingkup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asas dan Prinsip Pemrosesan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jenis dan Klasifikasi Data Pribadi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hak Subjek Data Pribadi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dasar Pemrosesan dan Persetujuan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aktivitas Pemrosesan dan Pengumpulan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Pribadi Anak dan Kelompok Rentan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kualitas, Akurasi, dan Pembaruan Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akuntabilitas, Pencatatan, dan Tata Kelola Kepatuhan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keamanan, Kerahasiaan, dan Penanganan Insiden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retensi, Penghentian, Penghapusan, dan Pemusnahan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pengecualian dan Pembatasan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transfer dan Pengalihan Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Larangan dan Perbuatan Melawan Hukum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akses dan Pemanfaatan Data Pemerintah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urgensi, Konsep, dan Landasan Pelindungan Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rujukan Regulasi Lain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lainnya (wajib jelaskan di V12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Larangan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kewajiban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pengecualian atau pembatasan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kebolehan atau kewenangan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definisi, klasifikasi, atau ruang lingkup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asas, prinsip, atau tujuan umum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deskriptif, argumentatif, atau rekomendasi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rujukan atau daftar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perencanaan dan dasar pemrosesan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pengumpulan atau akuisisi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pengolahan dan analisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penyimpanan dan pengamanan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penyebarluasan dan transfer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retensi dan penghapusan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata kelola dan hak subjek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lintas tahap atau tidak spesifik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-fungsional: keamanan dan kerahasiaan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-fungsional: mutu data, kepatuhan, dan akuntabilitas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fungsional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Batasan atau aturan bisnis hukum</t>
   </si>
   <si>
     <t xml:space="preserve">Tidak menghasilkan kebutuhan</t>
@@ -1172,7 +1283,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1236,6 +1347,57 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1328,7 +1490,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1409,11 +1571,39 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1421,7 +1611,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2030,7 +2220,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="true">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:S86"/>
@@ -2040,8 +2230,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="11.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="17.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="66.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="1" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="25.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="11" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="11" width="25.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="25.57"/>
@@ -2107,7 +2297,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="n">
         <v>2</v>
       </c>
@@ -2154,7 +2344,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="n">
         <v>3</v>
       </c>
@@ -2201,7 +2391,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="n">
         <v>4</v>
       </c>
@@ -2248,7 +2438,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="n">
         <v>5</v>
       </c>
@@ -2295,7 +2485,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="n">
         <v>6</v>
       </c>
@@ -2342,7 +2532,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="n">
         <v>7</v>
       </c>
@@ -2389,7 +2579,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="n">
         <v>8</v>
       </c>
@@ -2436,7 +2626,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="n">
         <v>9</v>
       </c>
@@ -2483,7 +2673,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="n">
         <v>10</v>
       </c>
@@ -2530,7 +2720,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="n">
         <v>11</v>
       </c>
@@ -2577,7 +2767,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="n">
         <v>12</v>
       </c>
@@ -2644,25 +2834,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A13)="","",INDEX(Korpus!$F:$F,$A13))</f>
         <v>Dalam Pasal 28 G ayat (1) disebutkan bahwa “Setiap orang berhak atas perlindungan diri pribadi, data juga berhubungan dengan konsep hak keluarga, kehormatan, martabat, dan harta benda yang di bawah kekuasaannya, serta berhak atas rasa aman dan perlindungan dari ancaman ketakutan untuk berbuat atau tidak berbuat sesuatu yang merupakan hak asasi.”</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="18" t="s">
+      <c r="J13" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="20" t="s">
         <v>68</v>
       </c>
       <c r="M13" s="19"/>
@@ -2687,7 +2877,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="n">
         <v>14</v>
       </c>
@@ -2734,7 +2924,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="n">
         <v>15</v>
       </c>
@@ -2781,7 +2971,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="n">
         <v>16</v>
       </c>
@@ -2828,7 +3018,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="n">
         <v>17</v>
       </c>
@@ -2875,7 +3065,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="n">
         <v>18</v>
       </c>
@@ -2922,7 +3112,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="n">
         <v>19</v>
       </c>
@@ -2969,7 +3159,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="n">
         <v>20</v>
       </c>
@@ -3036,25 +3226,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A21)="","",INDEX(Korpus!$F:$F,$A21))</f>
         <v>Selain itu Peraturan OJK Nomor 13 Tahun 2018 Tentang Inovasi Keuangan Digital di Sektor Keuangan, telah memasukkan poin terkait perlindungan dan kerahasiaan data.</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H21" s="18" t="s">
+      <c r="H21" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="I21" s="18" t="s">
+      <c r="I21" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="J21" s="18" t="s">
+      <c r="J21" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="K21" s="18" t="s">
+      <c r="K21" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="L21" s="18"/>
+      <c r="L21" s="20"/>
       <c r="M21" s="19"/>
       <c r="N21" s="19"/>
       <c r="O21" s="15" t="s">
@@ -3077,7 +3267,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="n">
         <v>22</v>
       </c>
@@ -3124,7 +3314,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="n">
         <v>23</v>
       </c>
@@ -3171,7 +3361,7 @@
         <v>5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="n">
         <v>24</v>
       </c>
@@ -3238,25 +3428,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A25)="","",INDEX(Korpus!$F:$F,$A25))</f>
         <v>Selain itu juga sudah ada Peraturan Menteri Nomor 20 Tahun 2016 tentang Perlindungan Data Pribadi namun belum cukup memberikan perlindungan kepada konsumen.</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="H25" s="18" t="s">
+      <c r="H25" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I25" s="18" t="s">
+      <c r="I25" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="J25" s="18" t="s">
+      <c r="J25" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="K25" s="18" t="s">
+      <c r="K25" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="L25" s="18"/>
+      <c r="L25" s="20"/>
       <c r="M25" s="19"/>
       <c r="N25" s="19"/>
       <c r="O25" s="15" t="s">
@@ -3279,7 +3469,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="n">
         <v>26</v>
       </c>
@@ -3326,7 +3516,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="n">
         <v>27</v>
       </c>
@@ -3373,7 +3563,7 @@
         <v>Bagian KesatuIdentitas Anak</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="n">
         <v>28</v>
       </c>
@@ -3420,7 +3610,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="n">
         <v>29</v>
       </c>
@@ -3467,7 +3657,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="n">
         <v>30</v>
       </c>
@@ -3514,7 +3704,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="n">
         <v>31</v>
       </c>
@@ -3561,7 +3751,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="n">
         <v>32</v>
       </c>
@@ -3608,7 +3798,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="n">
         <v>33</v>
       </c>
@@ -3655,7 +3845,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="n">
         <v>34</v>
       </c>
@@ -3722,25 +3912,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A35)="","",INDEX(Korpus!$F:$F,$A35))</f>
         <v>Subjek Data Pribadi berhak untuk mengakhiri pemrosesan, menghapus, dan/ atau memusnahkan Data Pribadi tentang dirinya sesuai dengan ketentuan peraturan perundang-undangan.</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="G35" s="18" t="s">
+      <c r="G35" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H35" s="18" t="s">
+      <c r="H35" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="I35" s="18" t="s">
+      <c r="I35" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="J35" s="18" t="s">
+      <c r="J35" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="K35" s="18" t="s">
+      <c r="K35" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="L35" s="18"/>
+      <c r="L35" s="20"/>
       <c r="M35" s="19"/>
       <c r="N35" s="19"/>
       <c r="O35" s="15" t="s">
@@ -3763,7 +3953,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="n">
         <v>36</v>
       </c>
@@ -3810,7 +4000,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="n">
         <v>37</v>
       </c>
@@ -3857,7 +4047,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="n">
         <v>38</v>
       </c>
@@ -3904,7 +4094,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="n">
         <v>39</v>
       </c>
@@ -3951,7 +4141,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="n">
         <v>40</v>
       </c>
@@ -3998,7 +4188,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="n">
         <v>41</v>
       </c>
@@ -4065,25 +4255,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A42)="","",INDEX(Korpus!$F:$F,$A42))</f>
         <v>(1) Hak-hak Subjek Data Pribadi sebagaimana dimaksud dalam Pasal 8, Pasal 9, Pasal 10 ayat (1), Pasal 11, dan Pasal 13 ayat (1) dan ayat (2) dikecualikan untuk:a. kepentingan pertahanan dan keamanan nasional; b. kepentingan proses penegakan hukum; c. kepentingan umum dalam rangka penyelenggaraan negara; d. kepentingan pengawasan sektor jasa keuangan, moneter, sistem pembayaran, dan stabilitas sistem keuangan yang dilakukan dalam rangka penyelenggaraan negara; atau e. kepentingan statistik dan penelitian ilmiah. (2) Pengecualian sebagaimana dimaksud pada ayat (1) dilaksanakan hanya dalam rangka pelaksanaan ketentuan Undang-Undang.</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="G42" s="18" t="s">
+      <c r="G42" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H42" s="18" t="s">
+      <c r="H42" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="I42" s="18" t="s">
+      <c r="I42" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="J42" s="18" t="s">
+      <c r="J42" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="K42" s="18" t="s">
+      <c r="K42" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="L42" s="18"/>
+      <c r="L42" s="20"/>
       <c r="M42" s="19"/>
       <c r="N42" s="19"/>
       <c r="O42" s="15" t="s">
@@ -4106,7 +4296,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="n">
         <v>43</v>
       </c>
@@ -4173,25 +4363,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A44)="","",INDEX(Korpus!$F:$F,$A44))</f>
         <v>(1) Pemasangan alat pemroses atau pengolah data visual di tempat umum dan/ atau pada fasilitas pelayanan publik dilakukan dengan ketentuan: a. untuk tujuan keamanan, pencegahan bencana, lalu lintas atau dan/atau pengumpulan, analisis, dan pengaturan Informasi lalu lintas; b. harus Informasi pada area yang telah dipasang alat pemroses atau pengolah data visual; dan c. tidak digunakan untuk seseorang. (2) Ketentuan sebagaimana dimaksud pada ayat (1) huruf b dan huruf c dikecualikan untuk pencegahan tindak pidana dan proses penegakan hukum sesuai dengan ketentuan peraturan perundang-undangan.</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="G44" s="18" t="s">
+      <c r="G44" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="H44" s="18" t="s">
+      <c r="H44" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="I44" s="18" t="s">
+      <c r="I44" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="J44" s="18" t="s">
+      <c r="J44" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="K44" s="18" t="s">
+      <c r="K44" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="L44" s="18"/>
+      <c r="L44" s="20"/>
       <c r="M44" s="19"/>
       <c r="N44" s="19"/>
       <c r="O44" s="15" t="s">
@@ -4214,7 +4404,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="n">
         <v>45</v>
       </c>
@@ -4261,7 +4451,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="n">
         <v>46</v>
       </c>
@@ -4308,7 +4498,7 @@
         <v>Bagian KesatuUmum</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="n">
         <v>47</v>
       </c>
@@ -4355,7 +4545,7 @@
         <v>Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="n">
         <v>48</v>
       </c>
@@ -4402,7 +4592,7 @@
         <v>Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="n">
         <v>49</v>
       </c>
@@ -4449,7 +4639,7 @@
         <v>Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="n">
         <v>50</v>
       </c>
@@ -4496,7 +4686,7 @@
         <v>Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="n">
         <v>51</v>
       </c>
@@ -4563,25 +4753,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A52)="","",INDEX(Korpus!$F:$F,$A52))</f>
         <v>(1) Pemrosesan Data Pribadi anak secara khusus.(2) Pemrosesan Data Pribadi anak sebagaimana dimaksud pada ayat (1) wajib mendapat persetujuan dari orang tua anak dan/ atau wali anak sesuai dengan ketentuan peraturan perundang-undangan.</v>
       </c>
-      <c r="F52" s="18" t="s">
+      <c r="F52" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="G52" s="18" t="s">
+      <c r="G52" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H52" s="18" t="s">
+      <c r="H52" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="I52" s="18" t="s">
+      <c r="I52" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="J52" s="18" t="s">
+      <c r="J52" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="K52" s="18" t="s">
+      <c r="K52" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="L52" s="18"/>
+      <c r="L52" s="20"/>
       <c r="M52" s="19"/>
       <c r="N52" s="19"/>
       <c r="O52" s="15" t="s">
@@ -4604,7 +4794,7 @@
         <v>Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="n">
         <v>53</v>
       </c>
@@ -4671,25 +4861,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A54)="","",INDEX(Korpus!$F:$F,$A54))</f>
         <v>Pengendali Data Pribadi wajib melakukan pemrosesan Data Pribadi secara terbatas dan spesifik, sah secara hukum, dan transparan.</v>
       </c>
-      <c r="F54" s="18" t="s">
+      <c r="F54" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="G54" s="18" t="s">
+      <c r="G54" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H54" s="18" t="s">
+      <c r="H54" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="I54" s="18" t="s">
+      <c r="I54" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="J54" s="18" t="s">
+      <c r="J54" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="K54" s="18" t="s">
+      <c r="K54" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="L54" s="18"/>
+      <c r="L54" s="20"/>
       <c r="M54" s="19"/>
       <c r="N54" s="19"/>
       <c r="O54" s="15" t="s">
@@ -4712,7 +4902,7 @@
         <v>Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="n">
         <v>55</v>
       </c>
@@ -4779,25 +4969,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A56)="","",INDEX(Korpus!$F:$F,$A56))</f>
         <v>(1) Pengendali Data Pribadi wajib memastikan akurasi, kelengkapan, dan konsistensi Data Pribadi sesuai dengan ketentuan peraturan perundang-undangan.(2) Dalam memastikan akurasi, kelengkapan, dan konsistensi Data Pribadi sebagaimana dimaksud pada ayat (1) Pengendali Data Pribadi wajib melakukan verifikasi.</v>
       </c>
-      <c r="F56" s="18" t="s">
+      <c r="F56" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="G56" s="18" t="s">
+      <c r="G56" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H56" s="18" t="s">
+      <c r="H56" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="I56" s="18" t="s">
+      <c r="I56" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="J56" s="18" t="s">
+      <c r="J56" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="K56" s="18" t="s">
+      <c r="K56" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="L56" s="18"/>
+      <c r="L56" s="20"/>
       <c r="M56" s="19"/>
       <c r="N56" s="19"/>
       <c r="O56" s="15" t="s">
@@ -4820,7 +5010,7 @@
         <v>Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="90" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="n">
         <v>57</v>
       </c>
@@ -4867,7 +5057,7 @@
         <v>Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="n">
         <v>58</v>
       </c>
@@ -4914,7 +5104,7 @@
         <v>Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="n">
         <v>59</v>
       </c>
@@ -4961,7 +5151,7 @@
         <v>Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="n">
         <v>60</v>
       </c>
@@ -5008,7 +5198,7 @@
         <v>Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="n">
         <v>61</v>
       </c>
@@ -5055,7 +5245,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="n">
         <v>62</v>
       </c>
@@ -5102,7 +5292,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="n">
         <v>63</v>
       </c>
@@ -5149,7 +5339,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="n">
         <v>64</v>
       </c>
@@ -5196,7 +5386,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="n">
         <v>65</v>
       </c>
@@ -5243,7 +5433,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="15" t="n">
         <v>66</v>
       </c>
@@ -5290,7 +5480,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="15" t="n">
         <v>67</v>
       </c>
@@ -5337,7 +5527,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="15" t="n">
         <v>68</v>
       </c>
@@ -5384,7 +5574,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="15" t="n">
         <v>69</v>
       </c>
@@ -5451,25 +5641,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A70)="","",INDEX(Korpus!$F:$F,$A70))</f>
         <v>(1) Pengendali Data Pribadi wajib menghapus Data Pribadi dalam hal:a. Data Pribadi tidak lagi diperlukan untuk pencapaian tujuan pemrosesan Data Pribadi; b. Subjek Data Pribadi telah melakukan penarikan kembali persetujuan pemrosesan Data Pribadi; c. terdapat permintaan dari Subjek Data Pribadi; atau d. Data Pribadi diperoleh dan/ atau diproses dengan cara melawan hukum.(2) Data Pribadi sebagaimana dimaksud pada ayat (1) dilakukan sesuai dengan ketentuan peraturan perundang-undangan.</v>
       </c>
-      <c r="F70" s="18" t="s">
+      <c r="F70" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="G70" s="18" t="s">
+      <c r="G70" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H70" s="18" t="s">
+      <c r="H70" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="I70" s="18" t="s">
+      <c r="I70" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="J70" s="18" t="s">
+      <c r="J70" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="K70" s="18" t="s">
+      <c r="K70" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="L70" s="18"/>
+      <c r="L70" s="20"/>
       <c r="M70" s="19"/>
       <c r="N70" s="19"/>
       <c r="O70" s="15" t="s">
@@ -5492,7 +5682,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="15" t="n">
         <v>71</v>
       </c>
@@ -5539,7 +5729,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="15" t="n">
         <v>72</v>
       </c>
@@ -5586,7 +5776,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="15" t="n">
         <v>73</v>
       </c>
@@ -5633,7 +5823,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="15" t="n">
         <v>74</v>
       </c>
@@ -5680,7 +5870,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="15" t="n">
         <v>75</v>
       </c>
@@ -5727,7 +5917,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="15" t="n">
         <v>76</v>
       </c>
@@ -5774,7 +5964,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="15" t="n">
         <v>77</v>
       </c>
@@ -5821,7 +6011,7 @@
         <v>Bagian KeduaKewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="15" t="n">
         <v>78</v>
       </c>
@@ -5888,25 +6078,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A79)="","",INDEX(Korpus!$F:$F,$A79))</f>
         <v>Ketentuan mengenai kewajiban Pengendali Data Pribadi sebagaimana dimaksud dalam Pasal 29, Pasal 31, Pasal 35, Pasal 36, Pasal 37, Pasal 38, dan Pasal 39 berlaku juga terhadap Prosesor Data Pribadi.</v>
       </c>
-      <c r="F79" s="18" t="s">
+      <c r="F79" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="G79" s="18" t="s">
+      <c r="G79" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="H79" s="18" t="s">
+      <c r="H79" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="I79" s="18" t="s">
+      <c r="I79" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="J79" s="18" t="s">
+      <c r="J79" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="K79" s="18" t="s">
+      <c r="K79" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="L79" s="18"/>
+      <c r="L79" s="20"/>
       <c r="M79" s="19"/>
       <c r="N79" s="19"/>
       <c r="O79" s="15" t="s">
@@ -5929,7 +6119,7 @@
         <v>Bagian KetigaKewajiban Prosesor Data Pribadi</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="15" t="n">
         <v>80</v>
       </c>
@@ -5996,25 +6186,25 @@
         <f aca="false">IF(INDEX(Korpus!$F:$F,$A81)="","",INDEX(Korpus!$F:$F,$A81))</f>
         <v>(1) Pengendali Data Pribadi dapat melakukan transfer Data Pribadi kepada Pengendali Data Pribadi lainnya dalam wilayah hukum Negara Republik Indonesia.(2) Pengendali Data Pribadi yang melakukan transfer Data Pribadi dan yang menerima transfer Data Pribadi wajib melakukan Pelindungan Data Pribadi sebagaimana dimaksud dalam Undang-Undang ini.</v>
       </c>
-      <c r="F81" s="18" t="s">
+      <c r="F81" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="G81" s="18" t="s">
+      <c r="G81" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H81" s="18" t="s">
+      <c r="H81" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="I81" s="18" t="s">
+      <c r="I81" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="J81" s="18" t="s">
+      <c r="J81" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="K81" s="18" t="s">
+      <c r="K81" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="L81" s="18"/>
+      <c r="L81" s="20"/>
       <c r="M81" s="19"/>
       <c r="N81" s="19"/>
       <c r="O81" s="15" t="s">
@@ -6037,7 +6227,7 @@
         <v>Bagian KesatuTransfer Data Pribadi Dalam Wilayah Hukum Negara Republik Indonesia</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="15" t="n">
         <v>82</v>
       </c>
@@ -6084,7 +6274,7 @@
         <v>Bagian Kedua</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="15" t="n">
         <v>83</v>
       </c>
@@ -6131,7 +6321,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="15" t="n">
         <v>84</v>
       </c>
@@ -6178,7 +6368,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="15" t="n">
         <v>85</v>
       </c>
@@ -6225,7 +6415,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="60" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="15" t="n">
         <v>86</v>
       </c>
@@ -6273,13 +6463,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S86">
-    <filterColumn colId="14">
-      <filters>
-        <filter val="Ya"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S86"/>
   <conditionalFormatting sqref="Q2:Q86">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>Q2="OK"</formula>
@@ -6295,31 +6479,31 @@
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation allowBlank="true" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F86" type="list">
-      <formula1>'Daftar Kode'!$B$5:$B$13</formula1>
+      <formula1>'Daftar Kode'!$D$5:$D$13</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G2:G86" type="list">
-      <formula1>'Daftar Kode'!$B$16:$B$18</formula1>
+      <formula1>'Daftar Kode'!$D$16:$D$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H86" type="list">
-      <formula1>'Daftar Kode'!$B$21:$B$38</formula1>
+      <formula1>'Daftar Kode'!$D$21:$D$38</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I2:I86" type="list">
-      <formula1>'Daftar Kode'!$B$41:$B$49</formula1>
+      <formula1>'Daftar Kode'!$D$41:$D$49</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J2:J86" type="list">
-      <formula1>'Daftar Kode'!$B$52:$B$59</formula1>
+      <formula1>'Daftar Kode'!$D$52:$D$59</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K86" type="list">
-      <formula1>'Daftar Kode'!$B$62:$B$66</formula1>
+      <formula1>'Daftar Kode'!$D$62:$D$66</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L86" type="list">
-      <formula1>'Daftar Kode'!$B$21:$B$37</formula1>
+      <formula1>'Daftar Kode'!$D$21:$D$37</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -6339,660 +6523,894 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="21" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="21" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="21" width="51.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="21" width="58.38"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="22" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="23" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="24" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="25" t="s">
         <v>103</v>
       </c>
+      <c r="D4" s="26" t="str">
+        <f aca="false">$B4 &amp; " - " &amp; $C4</f>
+        <v>Kode - Label</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="28" t="s">
         <v>104</v>
       </c>
+      <c r="C5" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="21" t="str">
+        <f aca="false">$B5 &amp; " - " &amp; $C5</f>
+        <v>S1 - Pengendali Data Pribadi</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="20" t="s">
+      <c r="B6" s="28" t="s">
         <v>106</v>
       </c>
+      <c r="C6" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="21" t="str">
+        <f aca="false">$B6 &amp; " - " &amp; $C6</f>
+        <v>S2 - Prosesor Data Pribadi</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>107</v>
+      <c r="B7" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="21" t="str">
+        <f aca="false">$B7 &amp; " - " &amp; $C7</f>
+        <v>S3 - Pengendali dan Prosesor</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>108</v>
+      <c r="B8" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="21" t="str">
+        <f aca="false">$B8 &amp; " - " &amp; $C8</f>
+        <v>S4 - Subjek Data Pribadi</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>109</v>
+      <c r="B9" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="21" t="str">
+        <f aca="false">$B9 &amp; " - " &amp; $C9</f>
+        <v>S5 - Setiap Orang atau pihak umum</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>111</v>
+      <c r="B10" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="21" t="str">
+        <f aca="false">$B10 &amp; " - " &amp; $C10</f>
+        <v>S6 - Instansi atau Badan Publik</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>113</v>
+      <c r="B11" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="21" t="str">
+        <f aca="false">$B11 &amp; " - " &amp; $C11</f>
+        <v>S7 - Lembaga atau Pemerintah (otoritas)</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>115</v>
+      <c r="B12" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="21" t="str">
+        <f aca="false">$B12 &amp; " - " &amp; $C12</f>
+        <v>S8 - Penyelenggara sektor atau pihak lain</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>116</v>
+      <c r="B13" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="21" t="str">
+        <f aca="false">$B13 &amp; " - " &amp; $C13</f>
+        <v>S9 - Tidak ada subjek eksplisit</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="25" t="s">
         <v>103</v>
       </c>
+      <c r="D15" s="26" t="str">
+        <f aca="false">$B15 &amp; " - " &amp; $C15</f>
+        <v>Kode - Label</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>117</v>
+      <c r="B16" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="21" t="str">
+        <f aca="false">$B16 &amp; " - " &amp; $C16</f>
+        <v>R0 - Tidak relevan</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>118</v>
+      <c r="B17" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="21" t="str">
+        <f aca="false">$B17 &amp; " - " &amp; $C17</f>
+        <v>R1 - Relevan tidak langsung</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>119</v>
+      <c r="B18" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="21" t="str">
+        <f aca="false">$B18 &amp; " - " &amp; $C18</f>
+        <v>R2 - Relevan langsung</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="25" t="s">
         <v>103</v>
       </c>
+      <c r="D20" s="26" t="str">
+        <f aca="false">$B20 &amp; " - " &amp; $C20</f>
+        <v>Kode - Label</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>120</v>
+      <c r="B21" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="21" t="str">
+        <f aca="false">$B21 &amp; " - " &amp; $C21</f>
+        <v>T01 - Definisi, Istilah, dan Ruang Lingkup</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>121</v>
+      <c r="B22" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="21" t="str">
+        <f aca="false">$B22 &amp; " - " &amp; $C22</f>
+        <v>T02 - Asas dan Prinsip Pemrosesan</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>123</v>
+      <c r="B23" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" s="21" t="str">
+        <f aca="false">$B23 &amp; " - " &amp; $C23</f>
+        <v>T03 - Jenis dan Klasifikasi Data Pribadi</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>125</v>
+      <c r="B24" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" s="21" t="str">
+        <f aca="false">$B24 &amp; " - " &amp; $C24</f>
+        <v>T04 - Hak Subjek Data Pribadi</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>127</v>
+      <c r="B25" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="21" t="str">
+        <f aca="false">$B25 &amp; " - " &amp; $C25</f>
+        <v>T05 - Dasar Pemrosesan dan Persetujuan</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>128</v>
+      <c r="B26" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" s="21" t="str">
+        <f aca="false">$B26 &amp; " - " &amp; $C26</f>
+        <v>T06 - Aktivitas Pemrosesan dan Pengumpulan</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>129</v>
+      <c r="B27" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="21" t="str">
+        <f aca="false">$B27 &amp; " - " &amp; $C27</f>
+        <v>T07 - Data Pribadi Anak dan Kelompok Rentan</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>131</v>
+      <c r="B28" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="21" t="str">
+        <f aca="false">$B28 &amp; " - " &amp; $C28</f>
+        <v>T08 - Kualitas, Akurasi, dan Pembaruan Data</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>132</v>
+      <c r="B29" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="D29" s="21" t="str">
+        <f aca="false">$B29 &amp; " - " &amp; $C29</f>
+        <v>T09 - Akuntabilitas, Pencatatan, dan Tata Kelola Kepatuhan</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>133</v>
+      <c r="B30" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="21" t="str">
+        <f aca="false">$B30 &amp; " - " &amp; $C30</f>
+        <v>T10 - Keamanan, Kerahasiaan, dan Penanganan Insiden</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>134</v>
+      <c r="B31" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" s="21" t="str">
+        <f aca="false">$B31 &amp; " - " &amp; $C31</f>
+        <v>T11 - Retensi, Penghentian, Penghapusan, dan Pemusnahan</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>136</v>
+      <c r="B32" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" s="21" t="str">
+        <f aca="false">$B32 &amp; " - " &amp; $C32</f>
+        <v>T12 - Pengecualian dan Pembatasan</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>137</v>
+      <c r="B33" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="21" t="str">
+        <f aca="false">$B33 &amp; " - " &amp; $C33</f>
+        <v>T13 - Transfer dan Pengalihan Data</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>138</v>
+      <c r="B34" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="D34" s="21" t="str">
+        <f aca="false">$B34 &amp; " - " &amp; $C34</f>
+        <v>T14 - Larangan dan Perbuatan Melawan Hukum</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>140</v>
+      <c r="B35" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" s="21" t="str">
+        <f aca="false">$B35 &amp; " - " &amp; $C35</f>
+        <v>T15 - Akses dan Pemanfaatan Data Pemerintah</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>141</v>
+      <c r="B36" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="21" t="str">
+        <f aca="false">$B36 &amp; " - " &amp; $C36</f>
+        <v>T16 - Urgensi, Konsep, dan Landasan Pelindungan Data</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>142</v>
+      <c r="B37" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="D37" s="21" t="str">
+        <f aca="false">$B37 &amp; " - " &amp; $C37</f>
+        <v>T17 - Rujukan Regulasi Lain</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>144</v>
+      <c r="B38" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="D38" s="21" t="str">
+        <f aca="false">$B38 &amp; " - " &amp; $C38</f>
+        <v>T99 - Lainnya (wajib jelaskan di V12)</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="25" t="s">
         <v>103</v>
       </c>
+      <c r="D40" s="26" t="str">
+        <f aca="false">$B40 &amp; " - " &amp; $C40</f>
+        <v>Kode - Label</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20" t="s">
+      <c r="A41" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>146</v>
+      <c r="B41" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="21" t="str">
+        <f aca="false">$B41 &amp; " - " &amp; $C41</f>
+        <v>P1 - Larangan</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="20" t="s">
+      <c r="A42" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>147</v>
+      <c r="B42" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" s="21" t="str">
+        <f aca="false">$B42 &amp; " - " &amp; $C42</f>
+        <v>P2 - Kewajiban</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="20" t="s">
+      <c r="A43" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>148</v>
+      <c r="B43" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="D43" s="21" t="str">
+        <f aca="false">$B43 &amp; " - " &amp; $C43</f>
+        <v>P3 - Hak</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="20" t="s">
+      <c r="A44" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>149</v>
+      <c r="B44" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="D44" s="21" t="str">
+        <f aca="false">$B44 &amp; " - " &amp; $C44</f>
+        <v>P4 - Pengecualian atau pembatasan</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20" t="s">
+      <c r="A45" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B45" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>150</v>
+      <c r="B45" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="D45" s="21" t="str">
+        <f aca="false">$B45 &amp; " - " &amp; $C45</f>
+        <v>P5 - Kebolehan atau kewenangan</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="20" t="s">
+      <c r="A46" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>151</v>
+      <c r="B46" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="D46" s="21" t="str">
+        <f aca="false">$B46 &amp; " - " &amp; $C46</f>
+        <v>P6 - Definisi, klasifikasi, atau ruang lingkup</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="20" t="s">
+      <c r="A47" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>152</v>
+      <c r="B47" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="C47" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="D47" s="21" t="str">
+        <f aca="false">$B47 &amp; " - " &amp; $C47</f>
+        <v>P7 - Asas, prinsip, atau tujuan umum</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="20" t="s">
+      <c r="A48" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>154</v>
+      <c r="B48" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="D48" s="21" t="str">
+        <f aca="false">$B48 &amp; " - " &amp; $C48</f>
+        <v>P8 - Deskriptif, argumentatif, atau rekomendasi</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="20" t="s">
+      <c r="A49" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B49" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>155</v>
+      <c r="B49" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="D49" s="21" t="str">
+        <f aca="false">$B49 &amp; " - " &amp; $C49</f>
+        <v>P9 - Rujukan atau daftar</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="25" t="s">
         <v>103</v>
       </c>
+      <c r="D51" s="26" t="str">
+        <f aca="false">$B51 &amp; " - " &amp; $C51</f>
+        <v>Kode - Label</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="20" t="s">
+      <c r="A52" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>156</v>
+      <c r="B52" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="C52" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="D52" s="21" t="str">
+        <f aca="false">$B52 &amp; " - " &amp; $C52</f>
+        <v>F1 - Perencanaan dan dasar pemrosesan</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="20" t="s">
+      <c r="A53" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B53" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>157</v>
+      <c r="B53" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C53" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="D53" s="21" t="str">
+        <f aca="false">$B53 &amp; " - " &amp; $C53</f>
+        <v>F2 - Pengumpulan atau akuisisi</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="20" t="s">
+      <c r="A54" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B54" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C54" s="20" t="s">
-        <v>158</v>
+      <c r="B54" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C54" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="D54" s="21" t="str">
+        <f aca="false">$B54 &amp; " - " &amp; $C54</f>
+        <v>F3 - Pengolahan dan analisis</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="20" t="s">
+      <c r="A55" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B55" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55" s="20" t="s">
-        <v>159</v>
+      <c r="B55" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="C55" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" s="21" t="str">
+        <f aca="false">$B55 &amp; " - " &amp; $C55</f>
+        <v>F4 - Penyimpanan dan pengamanan</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="20" t="s">
+      <c r="A56" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B56" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>161</v>
+      <c r="B56" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="C56" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="D56" s="21" t="str">
+        <f aca="false">$B56 &amp; " - " &amp; $C56</f>
+        <v>F5 - Penyebarluasan dan transfer</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="20" t="s">
+      <c r="A57" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B57" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C57" s="20" t="s">
-        <v>162</v>
+      <c r="B57" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="D57" s="21" t="str">
+        <f aca="false">$B57 &amp; " - " &amp; $C57</f>
+        <v>F6 - Retensi dan penghapusan</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="20" t="s">
+      <c r="A58" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B58" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C58" s="20" t="s">
-        <v>163</v>
+      <c r="B58" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="C58" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="D58" s="21" t="str">
+        <f aca="false">$B58 &amp; " - " &amp; $C58</f>
+        <v>F7 - Tata kelola dan hak subjek</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="20" t="s">
+      <c r="A59" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="C59" s="20" t="s">
-        <v>164</v>
+      <c r="B59" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="C59" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="D59" s="21" t="str">
+        <f aca="false">$B59 &amp; " - " &amp; $C59</f>
+        <v>F8 - Lintas tahap atau tidak spesifik</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="25" t="s">
         <v>103</v>
       </c>
+      <c r="D61" s="26" t="str">
+        <f aca="false">$B61 &amp; " - " &amp; $C61</f>
+        <v>Kode - Label</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="20" t="s">
+      <c r="A62" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B62" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="C62" s="20" t="s">
-        <v>166</v>
+      <c r="B62" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="C62" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="D62" s="21" t="str">
+        <f aca="false">$B62 &amp; " - " &amp; $C62</f>
+        <v>K1 - Non-fungsional: keamanan dan kerahasiaan</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="20" t="s">
+      <c r="A63" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B63" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C63" s="20" t="s">
-        <v>167</v>
+      <c r="B63" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="C63" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D63" s="21" t="str">
+        <f aca="false">$B63 &amp; " - " &amp; $C63</f>
+        <v>K2 - Non-fungsional: mutu data, kepatuhan, dan akuntabilitas</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="20" t="s">
+      <c r="A64" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B64" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>168</v>
+      <c r="B64" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C64" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="D64" s="21" t="str">
+        <f aca="false">$B64 &amp; " - " &amp; $C64</f>
+        <v>K3 - Fungsional</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="20" t="s">
+      <c r="A65" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B65" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C65" s="20" t="s">
-        <v>169</v>
+      <c r="B65" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C65" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="D65" s="21" t="str">
+        <f aca="false">$B65 &amp; " - " &amp; $C65</f>
+        <v>K4 - Batasan atau aturan bisnis hukum</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="20" t="s">
+      <c r="A66" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B66" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C66" s="20" t="s">
-        <v>170</v>
+      <c r="B66" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="D66" s="21" t="str">
+        <f aca="false">$B66 &amp; " - " &amp; $C66</f>
+        <v>K5 - Tidak menghasilkan kebutuhan</v>
       </c>
     </row>
   </sheetData>
@@ -7020,1494 +7438,1494 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" s="22" t="s">
+      <c r="A1" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="F1" s="22" t="s">
+      <c r="D1" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1" s="29" t="s">
         <v>56</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>184</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>191</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>233</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>239</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>243</v>
+        <v>280</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>244</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>245</v>
+        <v>282</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>246</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>248</v>
+        <v>285</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>258</v>
+        <v>295</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>260</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>262</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>265</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>269</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>272</v>
+        <v>309</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>276</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>281</v>
+        <v>318</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>282</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>284</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>285</v>
+        <v>322</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>287</v>
+        <v>324</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>288</v>
+        <v>325</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>295</v>
+        <v>332</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>297</v>
+        <v>334</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>299</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>301</v>
+        <v>338</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>304</v>
+        <v>341</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>306</v>
+        <v>343</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>308</v>
+        <v>345</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>310</v>
+        <v>347</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>312</v>
+        <v>349</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>314</v>
+        <v>351</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>316</v>
+        <v>353</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>318</v>
+        <v>355</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>320</v>
+        <v>357</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>322</v>
+        <v>359</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>323</v>
+        <v>360</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>324</v>
+        <v>361</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>326</v>
+        <v>363</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>328</v>
+        <v>365</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="F78" s="23" t="s">
-        <v>339</v>
+        <v>375</v>
+      </c>
+      <c r="F78" s="30" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>341</v>
+        <v>378</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>342</v>
+        <v>379</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>344</v>
+        <v>381</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="162.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>348</v>
+        <v>385</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>350</v>
+        <v>387</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>351</v>
+        <v>388</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>354</v>
+        <v>391</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>356</v>
+        <v>393</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>358</v>
+        <v>395</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>361</v>
+        <v>398</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>362</v>
+        <v>399</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>363</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
